--- a/data/personalia/II PD.xlsx
+++ b/data/personalia/II PD.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/047618f1b9410114/Desktop/p3ste-app/Fix/Personalia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="47" documentId="8_{2EC12D97-7331-4D7E-89F2-494686D0BEDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B7660EB2-8C58-44DB-B341-EFB3BBD11546}"/>
+  <xr:revisionPtr revIDLastSave="48" documentId="8_{2EC12D97-7331-4D7E-89F2-494686D0BEDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3BB1F7A2-FFF0-4AEF-93BA-E2C17DBA1017}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="81">
   <si>
     <t>Wilayah</t>
   </si>
@@ -187,9 +187,6 @@
     <t>RAHMAN DONGAN HARAHAP</t>
   </si>
   <si>
-    <t>EXSEL PRATAMA PUTRA</t>
-  </si>
-  <si>
     <t>Quality Controller</t>
   </si>
   <si>
@@ -266,9 +263,6 @@
   </si>
   <si>
     <t>PRP.080299.122705</t>
-  </si>
-  <si>
-    <t>PRP.230798.122704</t>
   </si>
   <si>
     <t>PMP.010789.65223</t>
@@ -661,7 +655,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T74"/>
+  <dimension ref="A1:T73"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="13.15" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="11.86328125" style="2" customWidth="1"/>
@@ -760,10 +754,10 @@
         <v>25</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>36</v>
@@ -787,7 +781,7 @@
         <v>47362</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R2" s="6">
         <v>46851</v>
@@ -810,7 +804,7 @@
         <v>35</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>36</v>
@@ -834,13 +828,13 @@
         <v>53175</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="O3" s="6">
         <v>46574</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="R3" s="6">
         <v>47008</v>
@@ -860,13 +854,13 @@
         <v>31</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H4" s="6">
         <v>45371</v>
@@ -887,13 +881,13 @@
         <v>54940</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="O4" s="6">
         <v>46011</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="R4" s="6">
         <v>47370</v>
@@ -913,13 +907,13 @@
         <v>32</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H5" s="6">
         <v>44927</v>
@@ -940,7 +934,7 @@
         <v>53509</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="O5" s="6">
         <v>46433</v>
@@ -960,13 +954,13 @@
         <v>32</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H6" s="6">
         <v>44927</v>
@@ -987,7 +981,7 @@
         <v>52505</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="O6" s="6">
         <v>46433</v>
@@ -1007,13 +1001,13 @@
         <v>33</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H7" s="6">
         <v>44927</v>
@@ -1034,7 +1028,7 @@
         <v>53297</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O7" s="6">
         <v>46448</v>
@@ -1054,13 +1048,13 @@
         <v>33</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H8" s="6">
         <v>44927</v>
@@ -1081,7 +1075,7 @@
         <v>55732</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="O8" s="6">
         <v>46851</v>
@@ -1101,13 +1095,13 @@
         <v>33</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H9" s="6">
         <v>44927</v>
@@ -1128,7 +1122,7 @@
         <v>56066</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O9" s="6">
         <v>46861</v>
@@ -1148,13 +1142,13 @@
         <v>33</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F10" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="G10" s="2" t="s">
         <v>64</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>65</v>
       </c>
       <c r="H10" s="6">
         <v>44927</v>
@@ -1175,7 +1169,7 @@
         <v>54514</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="O10" s="6">
         <v>46433</v>
@@ -1195,13 +1189,13 @@
         <v>33</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F11" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="G11" s="2" t="s">
         <v>64</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>65</v>
       </c>
       <c r="H11" s="6">
         <v>44927</v>
@@ -1222,7 +1216,7 @@
         <v>55854</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="O11" s="6">
         <v>46448</v>
@@ -1242,13 +1236,13 @@
         <v>33</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F12" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="G12" s="2" t="s">
         <v>64</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>65</v>
       </c>
       <c r="H12" s="6">
         <v>44927</v>
@@ -1269,7 +1263,7 @@
         <v>55001</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O12" s="6">
         <v>46433</v>
@@ -1289,13 +1283,13 @@
         <v>33</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F13" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="G13" s="2" t="s">
         <v>64</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>65</v>
       </c>
       <c r="H13" s="6">
         <v>44927</v>
@@ -1316,7 +1310,7 @@
         <v>55427</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="O13" s="6">
         <v>46851</v>
@@ -1336,13 +1330,13 @@
         <v>33</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F14" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="G14" s="2" t="s">
         <v>64</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>65</v>
       </c>
       <c r="H14" s="6">
         <v>44927</v>
@@ -1363,7 +1357,7 @@
         <v>53905</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O14" s="6">
         <v>46433</v>
@@ -1383,13 +1377,13 @@
         <v>33</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F15" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="G15" s="2" t="s">
         <v>64</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>65</v>
       </c>
       <c r="H15" s="6">
         <v>44927</v>
@@ -1410,58 +1404,15 @@
         <v>56858</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="O15" s="6">
         <v>46861</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.45">
-      <c r="A16" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C16" s="2">
-        <v>72249</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="H16" s="6">
-        <v>44927</v>
-      </c>
-      <c r="I16" s="2">
-        <v>5</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="K16" s="6">
-        <v>43286</v>
-      </c>
-      <c r="L16" s="6">
-        <v>35999</v>
-      </c>
-      <c r="M16" s="6">
-        <v>56462</v>
-      </c>
-      <c r="N16" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="O16" s="6">
-        <v>46861</v>
-      </c>
+      <c r="D16" s="2"/>
+      <c r="H16" s="6"/>
     </row>
     <row r="17" spans="4:16" x14ac:dyDescent="0.45">
       <c r="D17" s="2"/>
@@ -1510,11 +1461,11 @@
     <row r="28" spans="4:16" x14ac:dyDescent="0.45">
       <c r="D28" s="2"/>
       <c r="H28" s="6"/>
+      <c r="P28" s="8"/>
     </row>
     <row r="29" spans="4:16" x14ac:dyDescent="0.45">
       <c r="D29" s="2"/>
       <c r="H29" s="6"/>
-      <c r="P29" s="8"/>
     </row>
     <row r="30" spans="4:16" x14ac:dyDescent="0.45">
       <c r="D30" s="2"/>
@@ -1691,10 +1642,6 @@
     <row r="73" spans="4:8" x14ac:dyDescent="0.45">
       <c r="D73" s="2"/>
       <c r="H73" s="6"/>
-    </row>
-    <row r="74" spans="4:8" x14ac:dyDescent="0.45">
-      <c r="D74" s="2"/>
-      <c r="H74" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1706,19 +1653,19 @@
           <x14:formula1>
             <xm:f>LIST_DATA!$A$1:$A$9</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D1000</xm:sqref>
+          <xm:sqref>D2:D999</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0000-000001000000}">
           <x14:formula1>
             <xm:f>LIST_DATA!$B$1:$B$6</xm:f>
           </x14:formula1>
-          <xm:sqref>J2:J1000</xm:sqref>
+          <xm:sqref>J2:J999</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0000-000002000000}">
           <x14:formula1>
             <xm:f>LIST_DATA!$C$1:$C$15</xm:f>
           </x14:formula1>
-          <xm:sqref>I2:I1000</xm:sqref>
+          <xm:sqref>I2:I999</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/data/personalia/II PD.xlsx
+++ b/data/personalia/II PD.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/047618f1b9410114/Desktop/p3ste-app/Fix/Personalia/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\3. TSSP.3\18. STE APP\Personalia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="48" documentId="8_{2EC12D97-7331-4D7E-89F2-494686D0BEDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3BB1F7A2-FFF0-4AEF-93BA-E2C17DBA1017}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{637ED733-7FAB-4034-AC26-5FFCF62361F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,8 +16,20 @@
     <sheet name="Template Personalia" sheetId="1" r:id="rId1"/>
     <sheet name="LIST_DATA" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Template Personalia'!$A$1:$T$199</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -26,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="119">
   <si>
     <t>Wilayah</t>
   </si>
@@ -142,133 +154,247 @@
     <t>NIPP</t>
   </si>
   <si>
+    <t>Quality Controller</t>
+  </si>
+  <si>
+    <t>Kepala UPT Resor</t>
+  </si>
+  <si>
+    <t>Kaur UPT Resor</t>
+  </si>
+  <si>
+    <t>Petugas Negative Check</t>
+  </si>
+  <si>
+    <t>Kepala UPT Workshop</t>
+  </si>
+  <si>
+    <t>Kaur UPT Workshop</t>
+  </si>
+  <si>
+    <t>WS LAA Mri</t>
+  </si>
+  <si>
+    <t>LAA 1.4 Thb</t>
+  </si>
+  <si>
+    <t>Teknisi</t>
+  </si>
+  <si>
+    <t>LAA 1.1 Rk</t>
+  </si>
+  <si>
+    <t>LAA 1.14 Nmo</t>
+  </si>
+  <si>
+    <t>LAA 1.2 Prp</t>
+  </si>
+  <si>
+    <t>LAA 1.3 Srp</t>
+  </si>
+  <si>
+    <t>LAA 1.5 Du</t>
+  </si>
+  <si>
+    <t>LAA 1.11 Psm</t>
+  </si>
+  <si>
+    <t>LAA 1.6 Jakk</t>
+  </si>
+  <si>
+    <t>LAA 1.7 Pse</t>
+  </si>
+  <si>
+    <t>LAA 1.8 Mri</t>
+  </si>
+  <si>
+    <t>LAA 1.9 Jng</t>
+  </si>
+  <si>
+    <t>LAA 1.10 Ckr</t>
+  </si>
+  <si>
+    <t>LAA 1.12 Dp</t>
+  </si>
+  <si>
+    <t>LAA 1.13 Boo</t>
+  </si>
+  <si>
+    <t>LAA 1.15 Bst</t>
+  </si>
+  <si>
+    <t>PMP Lanjutan</t>
+  </si>
+  <si>
+    <t>PMP Pelaksana</t>
+  </si>
+  <si>
+    <t>PRP Pelaksana</t>
+  </si>
+  <si>
+    <t>PRP Lanjutan</t>
+  </si>
+  <si>
+    <t>Calon Pekerja</t>
+  </si>
+  <si>
+    <t>Calon Pelaksana</t>
+  </si>
+  <si>
+    <t>Calon Teknisi</t>
+  </si>
+  <si>
+    <t>Calon Pelaksana Workshop</t>
+  </si>
+  <si>
+    <t>Calon Petugas Negative Check</t>
+  </si>
+  <si>
+    <t>Executive Vice President</t>
+  </si>
+  <si>
+    <t>Kepala UPT BYST</t>
+  </si>
+  <si>
+    <t>Pelaksana Workshop</t>
+  </si>
+  <si>
+    <t>Subunit of Field Service Power System 1</t>
+  </si>
+  <si>
+    <t>Subunit of Field Service Power System 2</t>
+  </si>
+  <si>
+    <t>Subunit of Field Service Signalling And Communication 1</t>
+  </si>
+  <si>
+    <t>Subunit of Field Service Signalling And Communication 2</t>
+  </si>
+  <si>
+    <t>Subunit of Workshop And OCC Signalling and Communication</t>
+  </si>
+  <si>
+    <t>Subunit of Workshop Power System And OCC Power</t>
+  </si>
+  <si>
+    <t>Vice President</t>
+  </si>
+  <si>
     <t>II PD</t>
   </si>
   <si>
     <t>IDRUS</t>
   </si>
   <si>
+    <t>PLT QC STL Prasarana</t>
+  </si>
+  <si>
+    <t>PMP.170873.125654</t>
+  </si>
+  <si>
     <t>MUHAMMAD SUBARI</t>
   </si>
   <si>
+    <t>AM Fasilitas Jalan Rel, Jembatan dan Sintelis</t>
+  </si>
+  <si>
+    <t>PRP.010789.45604</t>
+  </si>
+  <si>
+    <t>PMP.010789.65223</t>
+  </si>
+  <si>
     <t>EDO SAPUTRA</t>
   </si>
   <si>
+    <t>Kepala UPT Resor STL Kelas C Pd</t>
+  </si>
+  <si>
+    <t>Pd</t>
+  </si>
+  <si>
+    <t>PRP.05031994.33019</t>
+  </si>
+  <si>
+    <t>PMP.050394.75603</t>
+  </si>
+  <si>
     <t>KHAHARDI ERNOF (STL)</t>
   </si>
   <si>
+    <t>Supervisor Perawatan Perbaikan UPT Resor Sintelis Kelas C Pd</t>
+  </si>
+  <si>
+    <t>PRP.300690.40876</t>
+  </si>
+  <si>
     <t>HANDY ARIEF YANTO (STL)</t>
   </si>
   <si>
+    <t>Supervisor Perawatan Preventif UPT Resor Sintelis Kelas C Pd</t>
+  </si>
+  <si>
+    <t>PRP.090787.02294</t>
+  </si>
+  <si>
     <t>ARNOF ZAHAR (STL)</t>
   </si>
   <si>
+    <t>PNC Perbaikan UPT Resor STL Pd</t>
+  </si>
+  <si>
+    <t>PRP.161189.41063</t>
+  </si>
+  <si>
     <t>ROZI SAPUTRA</t>
   </si>
   <si>
+    <t>PRP.170796.122707</t>
+  </si>
+  <si>
     <t>RAFES ANTONI</t>
   </si>
   <si>
+    <t>PRP.160697.122708</t>
+  </si>
+  <si>
     <t>ALMAN MARZUKI (STL)</t>
   </si>
   <si>
+    <t>PNC Preventif UPT Resor STL Pd</t>
+  </si>
+  <si>
+    <t>PRP.150393.40884</t>
+  </si>
+  <si>
     <t>RIZKI KURNIADI (STL)</t>
   </si>
   <si>
+    <t>PRP.141196.41062</t>
+  </si>
+  <si>
     <t>FAJAR RACHMAT HARIANDO (STL)</t>
   </si>
   <si>
+    <t>PRP.230794.40882</t>
+  </si>
+  <si>
     <t>RENGGA PUTRA GUCI</t>
   </si>
   <si>
+    <t>PRP.260995.122706</t>
+  </si>
+  <si>
     <t>ROLI SAPUTRA (STL)</t>
   </si>
   <si>
+    <t>PRP.300791.40676</t>
+  </si>
+  <si>
     <t>RAHMAN DONGAN HARAHAP</t>
   </si>
   <si>
-    <t>Quality Controller</t>
-  </si>
-  <si>
-    <t>Kepala UPT Resor</t>
-  </si>
-  <si>
-    <t>Kaur UPT Resor</t>
-  </si>
-  <si>
-    <t>Petugas Negative Check</t>
-  </si>
-  <si>
-    <t>PLT QC STL Prasarana</t>
-  </si>
-  <si>
-    <t>AM Fasilitas Jalan Rel, Jembatan dan Sintelis</t>
-  </si>
-  <si>
-    <t>Kepala UPT Resor STL Kelas C Pd</t>
-  </si>
-  <si>
-    <t>Supervisor Perawatan Perbaikan UPT Resor Sintelis Kelas C Pd</t>
-  </si>
-  <si>
-    <t>Supervisor Perawatan Preventif UPT Resor Sintelis Kelas C Pd</t>
-  </si>
-  <si>
-    <t>PNC Perbaikan UPT Resor STL Pd</t>
-  </si>
-  <si>
-    <t>PNC Preventif UPT Resor STL Pd</t>
-  </si>
-  <si>
-    <t>Pd</t>
-  </si>
-  <si>
-    <t>PMP.170873.125654</t>
-  </si>
-  <si>
-    <t>PRP.010789.45604</t>
-  </si>
-  <si>
-    <t>PRP.05031994.33019</t>
-  </si>
-  <si>
-    <t>PRP.300690.40876</t>
-  </si>
-  <si>
-    <t>PRP.090787.02294</t>
-  </si>
-  <si>
-    <t>PRP.161189.41063</t>
-  </si>
-  <si>
-    <t>PRP.170796.122707</t>
-  </si>
-  <si>
-    <t>PRP.160697.122708</t>
-  </si>
-  <si>
-    <t>PRP.150393.40884</t>
-  </si>
-  <si>
-    <t>PRP.141196.41062</t>
-  </si>
-  <si>
-    <t>PRP.230794.40882</t>
-  </si>
-  <si>
-    <t>PRP.260995.122706</t>
-  </si>
-  <si>
-    <t>PRP.300791.40676</t>
-  </si>
-  <si>
     <t>PRP.080299.122705</t>
-  </si>
-  <si>
-    <t>PMP.010789.65223</t>
-  </si>
-  <si>
-    <t>PMP.050394.75603</t>
   </si>
 </sst>
 </file>
@@ -339,9 +465,6 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -350,8 +473,11 @@
     <xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -655,30 +781,29 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T73"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="13.15" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:T200"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="13.15" zeroHeight="1" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="11.86328125" style="2" customWidth="1"/>
     <col min="2" max="2" width="27.265625" style="3" customWidth="1"/>
     <col min="3" max="3" width="7.86328125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="20.59765625" style="3" customWidth="1"/>
-    <col min="5" max="5" width="20.59765625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="32" style="4" customWidth="1"/>
-    <col min="7" max="7" width="8.46484375" style="2" customWidth="1"/>
-    <col min="8" max="8" width="13.1328125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="20.59765625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="21.53125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="32" style="7" customWidth="1"/>
+    <col min="7" max="7" width="12.1328125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="13.1328125" style="5" customWidth="1"/>
     <col min="9" max="9" width="7.06640625" style="2" customWidth="1"/>
     <col min="10" max="10" width="10.73046875" style="2" customWidth="1"/>
-    <col min="11" max="13" width="13.1328125" style="6" customWidth="1"/>
+    <col min="11" max="13" width="13.1328125" style="5" customWidth="1"/>
     <col min="14" max="14" width="22" style="2" customWidth="1"/>
-    <col min="15" max="15" width="13.1328125" style="6" customWidth="1"/>
-    <col min="16" max="16" width="22" style="3" customWidth="1"/>
-    <col min="17" max="17" width="22" style="2" customWidth="1"/>
-    <col min="18" max="18" width="13.1328125" style="6" customWidth="1"/>
-    <col min="19" max="20" width="22" style="3" customWidth="1"/>
+    <col min="15" max="15" width="13.1328125" style="5" customWidth="1"/>
+    <col min="16" max="17" width="22" style="2" customWidth="1"/>
+    <col min="18" max="18" width="13.1328125" style="5" customWidth="1"/>
+    <col min="19" max="20" width="22" style="2" customWidth="1"/>
     <col min="21" max="16384" width="9.06640625" style="3" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="5" customFormat="1" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:20" s="4" customFormat="1" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -700,7 +825,7 @@
       <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="6" t="s">
         <v>6</v>
       </c>
       <c r="I1" s="1" t="s">
@@ -709,19 +834,19 @@
       <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="K1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="L1" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="M1" s="6" t="s">
         <v>11</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="7" t="s">
+      <c r="O1" s="6" t="s">
         <v>13</v>
       </c>
       <c r="P1" s="1" t="s">
@@ -730,7 +855,7 @@
       <c r="Q1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="R1" s="7" t="s">
+      <c r="R1" s="6" t="s">
         <v>16</v>
       </c>
       <c r="S1" s="1" t="s">
@@ -742,10 +867,10 @@
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="C2" s="2">
         <v>43550</v>
@@ -754,16 +879,16 @@
         <v>25</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>57</v>
+        <v>38</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>82</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H2" s="6">
-        <v>45550</v>
+      <c r="H2" s="5">
+        <v>45884</v>
       </c>
       <c r="I2" s="2">
         <v>11</v>
@@ -771,28 +896,31 @@
       <c r="J2" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K2" s="6">
+      <c r="K2" s="5">
         <v>35217</v>
       </c>
-      <c r="L2" s="6">
+      <c r="L2" s="5">
         <v>26893</v>
       </c>
-      <c r="M2" s="6">
+      <c r="M2" s="5">
         <v>47362</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="R2" s="6">
+        <v>83</v>
+      </c>
+      <c r="R2" s="5">
         <v>46851</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:20" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>40</v>
+        <v>84</v>
       </c>
       <c r="C3" s="2">
         <v>64523</v>
@@ -803,13 +931,13 @@
       <c r="E3" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="F3" s="4" t="s">
-        <v>58</v>
+      <c r="F3" s="7" t="s">
+        <v>85</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H3" s="6">
+      <c r="H3" s="5">
         <v>45992</v>
       </c>
       <c r="I3" s="2">
@@ -818,34 +946,40 @@
       <c r="J3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K3" s="6">
+      <c r="K3" s="5">
         <v>41791</v>
       </c>
-      <c r="L3" s="6">
+      <c r="L3" s="5">
         <v>32690</v>
       </c>
-      <c r="M3" s="6">
+      <c r="M3" s="5">
         <v>53175</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="O3" s="6">
+        <v>86</v>
+      </c>
+      <c r="O3" s="5">
         <v>46574</v>
       </c>
+      <c r="P3" s="2" t="s">
+        <v>64</v>
+      </c>
       <c r="Q3" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="R3" s="6">
+        <v>87</v>
+      </c>
+      <c r="R3" s="5">
         <v>47008</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>41</v>
+        <v>88</v>
       </c>
       <c r="C4" s="2">
         <v>70533</v>
@@ -854,15 +988,15 @@
         <v>31</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>59</v>
+        <v>39</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>89</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="H4" s="6">
+        <v>90</v>
+      </c>
+      <c r="H4" s="5">
         <v>45371</v>
       </c>
       <c r="I4" s="2">
@@ -871,34 +1005,40 @@
       <c r="J4" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K4" s="6">
+      <c r="K4" s="5">
         <v>42646</v>
       </c>
-      <c r="L4" s="6">
-        <v>34457</v>
-      </c>
-      <c r="M4" s="6">
-        <v>54940</v>
+      <c r="L4" s="5">
+        <v>34398</v>
+      </c>
+      <c r="M4" s="5">
+        <v>54879</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="O4" s="6">
+        <v>91</v>
+      </c>
+      <c r="O4" s="5">
         <v>46011</v>
       </c>
+      <c r="P4" s="2" t="s">
+        <v>64</v>
+      </c>
       <c r="Q4" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="R4" s="6">
+        <v>92</v>
+      </c>
+      <c r="R4" s="5">
         <v>47370</v>
+      </c>
+      <c r="S4" s="2" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="5" spans="1:20" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>42</v>
+        <v>93</v>
       </c>
       <c r="C5" s="2">
         <v>68959</v>
@@ -907,16 +1047,16 @@
         <v>32</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>60</v>
+        <v>40</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>94</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="H5" s="6">
-        <v>44927</v>
+        <v>90</v>
+      </c>
+      <c r="H5" s="5">
+        <v>44575</v>
       </c>
       <c r="I5" s="2">
         <v>7</v>
@@ -924,28 +1064,31 @@
       <c r="J5" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K5" s="6">
-        <v>42681</v>
-      </c>
-      <c r="L5" s="6">
+      <c r="K5" s="5">
+        <v>42562</v>
+      </c>
+      <c r="L5" s="5">
         <v>33054</v>
       </c>
-      <c r="M5" s="6">
+      <c r="M5" s="5">
         <v>53509</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="O5" s="6">
+        <v>95</v>
+      </c>
+      <c r="O5" s="5">
         <v>46433</v>
+      </c>
+      <c r="P5" s="2" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="6" spans="1:20" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>43</v>
+        <v>96</v>
       </c>
       <c r="C6" s="2">
         <v>57107</v>
@@ -954,16 +1097,16 @@
         <v>32</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>61</v>
+        <v>40</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>97</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="H6" s="6">
-        <v>44927</v>
+        <v>90</v>
+      </c>
+      <c r="H6" s="5">
+        <v>44575</v>
       </c>
       <c r="I6" s="2">
         <v>7</v>
@@ -971,28 +1114,31 @@
       <c r="J6" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K6" s="6">
-        <v>40190</v>
-      </c>
-      <c r="L6" s="6">
-        <v>32027</v>
-      </c>
-      <c r="M6" s="6">
-        <v>52505</v>
+      <c r="K6" s="5">
+        <v>40513</v>
+      </c>
+      <c r="L6" s="5">
+        <v>31967</v>
+      </c>
+      <c r="M6" s="5">
+        <v>52444</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="O6" s="6">
+        <v>98</v>
+      </c>
+      <c r="O6" s="5">
         <v>46433</v>
+      </c>
+      <c r="P6" s="2" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>44</v>
+        <v>99</v>
       </c>
       <c r="C7" s="2">
         <v>68965</v>
@@ -1001,16 +1147,16 @@
         <v>33</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>62</v>
+        <v>41</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>100</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="H7" s="6">
-        <v>44927</v>
+        <v>90</v>
+      </c>
+      <c r="H7" s="5">
+        <v>44575</v>
       </c>
       <c r="I7" s="2">
         <v>5</v>
@@ -1018,28 +1164,31 @@
       <c r="J7" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K7" s="6">
-        <v>42681</v>
-      </c>
-      <c r="L7" s="6">
+      <c r="K7" s="5">
+        <v>42562</v>
+      </c>
+      <c r="L7" s="5">
         <v>32828</v>
       </c>
-      <c r="M7" s="6">
+      <c r="M7" s="5">
         <v>53297</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="O7" s="6">
+        <v>101</v>
+      </c>
+      <c r="O7" s="5">
         <v>46448</v>
+      </c>
+      <c r="P7" s="2" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>45</v>
+        <v>102</v>
       </c>
       <c r="C8" s="2">
         <v>72289</v>
@@ -1048,16 +1197,16 @@
         <v>33</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>62</v>
+        <v>41</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>100</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="H8" s="6">
-        <v>44927</v>
+        <v>90</v>
+      </c>
+      <c r="H8" s="5">
+        <v>44575</v>
       </c>
       <c r="I8" s="2">
         <v>5</v>
@@ -1065,28 +1214,31 @@
       <c r="J8" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K8" s="6">
-        <v>43286</v>
-      </c>
-      <c r="L8" s="6">
+      <c r="K8" s="5">
+        <v>43227</v>
+      </c>
+      <c r="L8" s="5">
         <v>35263</v>
       </c>
-      <c r="M8" s="6">
+      <c r="M8" s="5">
         <v>55732</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="O8" s="6">
+        <v>103</v>
+      </c>
+      <c r="O8" s="5">
         <v>46851</v>
+      </c>
+      <c r="P8" s="2" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A9" s="2" t="s">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>46</v>
+        <v>104</v>
       </c>
       <c r="C9" s="2">
         <v>72279</v>
@@ -1095,16 +1247,16 @@
         <v>33</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>62</v>
+        <v>41</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>100</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="H9" s="6">
-        <v>44927</v>
+        <v>90</v>
+      </c>
+      <c r="H9" s="5">
+        <v>44575</v>
       </c>
       <c r="I9" s="2">
         <v>5</v>
@@ -1112,28 +1264,31 @@
       <c r="J9" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K9" s="6">
-        <v>43286</v>
-      </c>
-      <c r="L9" s="6">
+      <c r="K9" s="5">
+        <v>43227</v>
+      </c>
+      <c r="L9" s="5">
         <v>35597</v>
       </c>
-      <c r="M9" s="6">
+      <c r="M9" s="5">
         <v>56066</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="O9" s="6">
+        <v>105</v>
+      </c>
+      <c r="O9" s="5">
         <v>46861</v>
+      </c>
+      <c r="P9" s="2" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A10" s="2" t="s">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>47</v>
+        <v>106</v>
       </c>
       <c r="C10" s="2">
         <v>68962</v>
@@ -1142,16 +1297,16 @@
         <v>33</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>63</v>
+        <v>41</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>107</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="H10" s="6">
-        <v>44927</v>
+        <v>90</v>
+      </c>
+      <c r="H10" s="5">
+        <v>43040</v>
       </c>
       <c r="I10" s="2">
         <v>5</v>
@@ -1159,28 +1314,31 @@
       <c r="J10" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K10" s="6">
-        <v>42681</v>
-      </c>
-      <c r="L10" s="6">
+      <c r="K10" s="5">
+        <v>42562</v>
+      </c>
+      <c r="L10" s="5">
         <v>34043</v>
       </c>
-      <c r="M10" s="6">
+      <c r="M10" s="5">
         <v>54514</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="O10" s="6">
+        <v>108</v>
+      </c>
+      <c r="O10" s="5">
         <v>46433</v>
+      </c>
+      <c r="P10" s="2" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A11" s="2" t="s">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>48</v>
+        <v>109</v>
       </c>
       <c r="C11" s="2">
         <v>68970</v>
@@ -1189,16 +1347,16 @@
         <v>33</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>63</v>
+        <v>41</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>107</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="H11" s="6">
-        <v>44927</v>
+        <v>90</v>
+      </c>
+      <c r="H11" s="5">
+        <v>44575</v>
       </c>
       <c r="I11" s="2">
         <v>5</v>
@@ -1206,28 +1364,31 @@
       <c r="J11" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K11" s="6">
-        <v>42681</v>
-      </c>
-      <c r="L11" s="6">
+      <c r="K11" s="5">
+        <v>42562</v>
+      </c>
+      <c r="L11" s="5">
         <v>35383</v>
       </c>
-      <c r="M11" s="6">
+      <c r="M11" s="5">
         <v>55854</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="O11" s="6">
+        <v>110</v>
+      </c>
+      <c r="O11" s="5">
         <v>46448</v>
+      </c>
+      <c r="P11" s="2" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A12" s="2" t="s">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>49</v>
+        <v>111</v>
       </c>
       <c r="C12" s="2">
         <v>68966</v>
@@ -1236,16 +1397,16 @@
         <v>33</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>63</v>
+        <v>41</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>107</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="H12" s="6">
-        <v>44927</v>
+        <v>90</v>
+      </c>
+      <c r="H12" s="5">
+        <v>43115</v>
       </c>
       <c r="I12" s="2">
         <v>5</v>
@@ -1253,28 +1414,31 @@
       <c r="J12" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K12" s="6">
-        <v>42681</v>
-      </c>
-      <c r="L12" s="6">
+      <c r="K12" s="5">
+        <v>42562</v>
+      </c>
+      <c r="L12" s="5">
         <v>34538</v>
       </c>
-      <c r="M12" s="6">
+      <c r="M12" s="5">
         <v>55001</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="O12" s="6">
+        <v>112</v>
+      </c>
+      <c r="O12" s="5">
         <v>46433</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A13" s="2" t="s">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>50</v>
+        <v>113</v>
       </c>
       <c r="C13" s="2">
         <v>72284</v>
@@ -1283,16 +1447,16 @@
         <v>33</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>63</v>
+        <v>41</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>107</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="H13" s="6">
-        <v>44927</v>
+        <v>90</v>
+      </c>
+      <c r="H13" s="5">
+        <v>43789</v>
       </c>
       <c r="I13" s="2">
         <v>5</v>
@@ -1300,28 +1464,31 @@
       <c r="J13" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K13" s="6">
-        <v>43286</v>
-      </c>
-      <c r="L13" s="6">
+      <c r="K13" s="5">
+        <v>43227</v>
+      </c>
+      <c r="L13" s="5">
         <v>34968</v>
       </c>
-      <c r="M13" s="6">
+      <c r="M13" s="5">
         <v>55427</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="O13" s="6">
+        <v>114</v>
+      </c>
+      <c r="O13" s="5">
         <v>46851</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A14" s="2" t="s">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>51</v>
+        <v>115</v>
       </c>
       <c r="C14" s="2">
         <v>68963</v>
@@ -1330,16 +1497,16 @@
         <v>33</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>63</v>
+        <v>41</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>107</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="H14" s="6">
-        <v>44927</v>
+        <v>90</v>
+      </c>
+      <c r="H14" s="5">
+        <v>44575</v>
       </c>
       <c r="I14" s="2">
         <v>5</v>
@@ -1347,28 +1514,31 @@
       <c r="J14" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K14" s="6">
-        <v>42681</v>
-      </c>
-      <c r="L14" s="6">
+      <c r="K14" s="5">
+        <v>42562</v>
+      </c>
+      <c r="L14" s="5">
         <v>33449</v>
       </c>
-      <c r="M14" s="6">
+      <c r="M14" s="5">
         <v>53905</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="O14" s="6">
+        <v>116</v>
+      </c>
+      <c r="O14" s="5">
         <v>46433</v>
+      </c>
+      <c r="P14" s="2" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A15" s="2" t="s">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>52</v>
+        <v>117</v>
       </c>
       <c r="C15" s="2">
         <v>72282</v>
@@ -1377,16 +1547,16 @@
         <v>33</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>63</v>
+        <v>41</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>107</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="H15" s="6">
-        <v>44927</v>
+        <v>90</v>
+      </c>
+      <c r="H15" s="5">
+        <v>43789</v>
       </c>
       <c r="I15" s="2">
         <v>5</v>
@@ -1394,278 +1564,252 @@
       <c r="J15" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K15" s="6">
-        <v>43286</v>
-      </c>
-      <c r="L15" s="6">
-        <v>36374</v>
-      </c>
-      <c r="M15" s="6">
-        <v>56858</v>
+      <c r="K15" s="5">
+        <v>43227</v>
+      </c>
+      <c r="L15" s="5">
+        <v>36199</v>
+      </c>
+      <c r="M15" s="5">
+        <v>56674</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="O15" s="6">
+        <v>118</v>
+      </c>
+      <c r="O15" s="5">
         <v>46861</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.45">
-      <c r="D16" s="2"/>
-      <c r="H16" s="6"/>
-    </row>
-    <row r="17" spans="4:16" x14ac:dyDescent="0.45">
-      <c r="D17" s="2"/>
-      <c r="H17" s="6"/>
-    </row>
-    <row r="18" spans="4:16" x14ac:dyDescent="0.45">
-      <c r="D18" s="2"/>
-      <c r="H18" s="6"/>
-    </row>
-    <row r="19" spans="4:16" x14ac:dyDescent="0.45">
-      <c r="D19" s="2"/>
-      <c r="H19" s="6"/>
-    </row>
-    <row r="20" spans="4:16" x14ac:dyDescent="0.45">
-      <c r="D20" s="2"/>
-      <c r="H20" s="6"/>
-    </row>
-    <row r="21" spans="4:16" x14ac:dyDescent="0.45">
-      <c r="D21" s="2"/>
-      <c r="H21" s="6"/>
-    </row>
-    <row r="22" spans="4:16" x14ac:dyDescent="0.45">
-      <c r="D22" s="2"/>
-      <c r="H22" s="6"/>
-    </row>
-    <row r="23" spans="4:16" x14ac:dyDescent="0.45">
-      <c r="D23" s="2"/>
-      <c r="H23" s="6"/>
-    </row>
-    <row r="24" spans="4:16" x14ac:dyDescent="0.45">
-      <c r="D24" s="2"/>
-      <c r="H24" s="6"/>
-    </row>
-    <row r="25" spans="4:16" x14ac:dyDescent="0.45">
-      <c r="D25" s="2"/>
-      <c r="H25" s="6"/>
-    </row>
-    <row r="26" spans="4:16" x14ac:dyDescent="0.45">
-      <c r="D26" s="2"/>
-      <c r="H26" s="6"/>
-    </row>
-    <row r="27" spans="4:16" x14ac:dyDescent="0.45">
-      <c r="D27" s="2"/>
-      <c r="H27" s="6"/>
-    </row>
-    <row r="28" spans="4:16" x14ac:dyDescent="0.45">
-      <c r="D28" s="2"/>
-      <c r="H28" s="6"/>
-      <c r="P28" s="8"/>
-    </row>
-    <row r="29" spans="4:16" x14ac:dyDescent="0.45">
-      <c r="D29" s="2"/>
-      <c r="H29" s="6"/>
-    </row>
-    <row r="30" spans="4:16" x14ac:dyDescent="0.45">
-      <c r="D30" s="2"/>
-      <c r="H30" s="6"/>
-    </row>
-    <row r="31" spans="4:16" x14ac:dyDescent="0.45">
-      <c r="D31" s="2"/>
-      <c r="H31" s="6"/>
-    </row>
-    <row r="32" spans="4:16" x14ac:dyDescent="0.45">
-      <c r="D32" s="2"/>
-      <c r="H32" s="6"/>
-    </row>
-    <row r="33" spans="4:8" x14ac:dyDescent="0.45">
-      <c r="D33" s="2"/>
-      <c r="H33" s="6"/>
-    </row>
-    <row r="34" spans="4:8" x14ac:dyDescent="0.45">
-      <c r="D34" s="2"/>
-      <c r="H34" s="6"/>
-    </row>
-    <row r="35" spans="4:8" x14ac:dyDescent="0.45">
-      <c r="D35" s="2"/>
-      <c r="H35" s="6"/>
-    </row>
-    <row r="36" spans="4:8" x14ac:dyDescent="0.45">
-      <c r="D36" s="2"/>
-      <c r="H36" s="6"/>
-    </row>
-    <row r="37" spans="4:8" x14ac:dyDescent="0.45">
-      <c r="D37" s="2"/>
-      <c r="H37" s="6"/>
-    </row>
-    <row r="38" spans="4:8" x14ac:dyDescent="0.45">
-      <c r="D38" s="2"/>
-      <c r="H38" s="6"/>
-    </row>
-    <row r="39" spans="4:8" x14ac:dyDescent="0.45">
-      <c r="D39" s="2"/>
-      <c r="H39" s="6"/>
-    </row>
-    <row r="40" spans="4:8" x14ac:dyDescent="0.45">
-      <c r="D40" s="2"/>
-      <c r="H40" s="6"/>
-    </row>
-    <row r="41" spans="4:8" x14ac:dyDescent="0.45">
-      <c r="D41" s="2"/>
-      <c r="H41" s="6"/>
-    </row>
-    <row r="42" spans="4:8" x14ac:dyDescent="0.45">
-      <c r="D42" s="2"/>
-      <c r="H42" s="6"/>
-    </row>
-    <row r="43" spans="4:8" x14ac:dyDescent="0.45">
-      <c r="D43" s="2"/>
-      <c r="H43" s="6"/>
-    </row>
-    <row r="44" spans="4:8" x14ac:dyDescent="0.45">
-      <c r="D44" s="2"/>
-      <c r="H44" s="6"/>
-    </row>
-    <row r="45" spans="4:8" x14ac:dyDescent="0.45">
-      <c r="D45" s="2"/>
-      <c r="H45" s="6"/>
-    </row>
-    <row r="46" spans="4:8" x14ac:dyDescent="0.45">
-      <c r="D46" s="2"/>
-      <c r="H46" s="6"/>
-    </row>
-    <row r="47" spans="4:8" x14ac:dyDescent="0.45">
-      <c r="D47" s="2"/>
-      <c r="H47" s="6"/>
-    </row>
-    <row r="48" spans="4:8" x14ac:dyDescent="0.45">
-      <c r="D48" s="2"/>
-      <c r="H48" s="6"/>
-    </row>
-    <row r="49" spans="4:8" x14ac:dyDescent="0.45">
-      <c r="D49" s="2"/>
-      <c r="H49" s="6"/>
-    </row>
-    <row r="50" spans="4:8" x14ac:dyDescent="0.45">
-      <c r="D50" s="2"/>
-      <c r="H50" s="6"/>
-    </row>
-    <row r="51" spans="4:8" x14ac:dyDescent="0.45">
-      <c r="D51" s="2"/>
-      <c r="H51" s="6"/>
-    </row>
-    <row r="52" spans="4:8" x14ac:dyDescent="0.45">
-      <c r="D52" s="2"/>
-      <c r="H52" s="6"/>
-    </row>
-    <row r="53" spans="4:8" x14ac:dyDescent="0.45">
-      <c r="D53" s="2"/>
-      <c r="H53" s="6"/>
-    </row>
-    <row r="54" spans="4:8" x14ac:dyDescent="0.45">
-      <c r="D54" s="2"/>
-      <c r="H54" s="6"/>
-    </row>
-    <row r="55" spans="4:8" x14ac:dyDescent="0.45">
-      <c r="D55" s="2"/>
-      <c r="H55" s="6"/>
-    </row>
-    <row r="56" spans="4:8" x14ac:dyDescent="0.45">
-      <c r="D56" s="2"/>
-      <c r="H56" s="6"/>
-    </row>
-    <row r="57" spans="4:8" x14ac:dyDescent="0.45">
-      <c r="D57" s="2"/>
-      <c r="H57" s="6"/>
-    </row>
-    <row r="58" spans="4:8" x14ac:dyDescent="0.45">
-      <c r="D58" s="2"/>
-      <c r="H58" s="6"/>
-    </row>
-    <row r="59" spans="4:8" x14ac:dyDescent="0.45">
-      <c r="D59" s="2"/>
-      <c r="H59" s="6"/>
-    </row>
-    <row r="60" spans="4:8" x14ac:dyDescent="0.45">
-      <c r="D60" s="2"/>
-      <c r="H60" s="6"/>
-    </row>
-    <row r="61" spans="4:8" x14ac:dyDescent="0.45">
-      <c r="D61" s="2"/>
-      <c r="H61" s="6"/>
-    </row>
-    <row r="62" spans="4:8" x14ac:dyDescent="0.45">
-      <c r="D62" s="2"/>
-      <c r="H62" s="6"/>
-    </row>
-    <row r="63" spans="4:8" x14ac:dyDescent="0.45">
-      <c r="D63" s="2"/>
-      <c r="H63" s="6"/>
-    </row>
-    <row r="64" spans="4:8" x14ac:dyDescent="0.45">
-      <c r="D64" s="2"/>
-      <c r="H64" s="6"/>
-    </row>
-    <row r="65" spans="4:8" x14ac:dyDescent="0.45">
-      <c r="D65" s="2"/>
-      <c r="H65" s="6"/>
-    </row>
-    <row r="66" spans="4:8" x14ac:dyDescent="0.45">
-      <c r="D66" s="2"/>
-      <c r="H66" s="6"/>
-    </row>
-    <row r="67" spans="4:8" x14ac:dyDescent="0.45">
-      <c r="D67" s="2"/>
-      <c r="H67" s="6"/>
-    </row>
-    <row r="68" spans="4:8" x14ac:dyDescent="0.45">
-      <c r="D68" s="2"/>
-      <c r="H68" s="6"/>
-    </row>
-    <row r="69" spans="4:8" x14ac:dyDescent="0.45">
-      <c r="D69" s="2"/>
-      <c r="H69" s="6"/>
-    </row>
-    <row r="70" spans="4:8" x14ac:dyDescent="0.45">
-      <c r="D70" s="2"/>
-      <c r="H70" s="6"/>
-    </row>
-    <row r="71" spans="4:8" x14ac:dyDescent="0.45">
-      <c r="D71" s="2"/>
-      <c r="H71" s="6"/>
-    </row>
-    <row r="72" spans="4:8" x14ac:dyDescent="0.45">
-      <c r="D72" s="2"/>
-      <c r="H72" s="6"/>
-    </row>
-    <row r="73" spans="4:8" x14ac:dyDescent="0.45">
-      <c r="D73" s="2"/>
-      <c r="H73" s="6"/>
-    </row>
+      <c r="P15" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.45"/>
+    <row r="17" x14ac:dyDescent="0.45"/>
+    <row r="18" x14ac:dyDescent="0.45"/>
+    <row r="19" x14ac:dyDescent="0.45"/>
+    <row r="20" x14ac:dyDescent="0.45"/>
+    <row r="21" x14ac:dyDescent="0.45"/>
+    <row r="22" x14ac:dyDescent="0.45"/>
+    <row r="23" x14ac:dyDescent="0.45"/>
+    <row r="24" x14ac:dyDescent="0.45"/>
+    <row r="25" x14ac:dyDescent="0.45"/>
+    <row r="26" x14ac:dyDescent="0.45"/>
+    <row r="27" x14ac:dyDescent="0.45"/>
+    <row r="28" x14ac:dyDescent="0.45"/>
+    <row r="29" x14ac:dyDescent="0.45"/>
+    <row r="30" x14ac:dyDescent="0.45"/>
+    <row r="31" x14ac:dyDescent="0.45"/>
+    <row r="32" x14ac:dyDescent="0.45"/>
+    <row r="33" x14ac:dyDescent="0.45"/>
+    <row r="34" x14ac:dyDescent="0.45"/>
+    <row r="35" x14ac:dyDescent="0.45"/>
+    <row r="36" x14ac:dyDescent="0.45"/>
+    <row r="37" x14ac:dyDescent="0.45"/>
+    <row r="38" x14ac:dyDescent="0.45"/>
+    <row r="39" x14ac:dyDescent="0.45"/>
+    <row r="40" x14ac:dyDescent="0.45"/>
+    <row r="41" x14ac:dyDescent="0.45"/>
+    <row r="42" x14ac:dyDescent="0.45"/>
+    <row r="43" x14ac:dyDescent="0.45"/>
+    <row r="44" x14ac:dyDescent="0.45"/>
+    <row r="45" x14ac:dyDescent="0.45"/>
+    <row r="46" x14ac:dyDescent="0.45"/>
+    <row r="47" x14ac:dyDescent="0.45"/>
+    <row r="48" x14ac:dyDescent="0.45"/>
+    <row r="49" x14ac:dyDescent="0.45"/>
+    <row r="50" x14ac:dyDescent="0.45"/>
+    <row r="51" x14ac:dyDescent="0.45"/>
+    <row r="52" x14ac:dyDescent="0.45"/>
+    <row r="53" x14ac:dyDescent="0.45"/>
+    <row r="54" x14ac:dyDescent="0.45"/>
+    <row r="55" x14ac:dyDescent="0.45"/>
+    <row r="56" x14ac:dyDescent="0.45"/>
+    <row r="57" x14ac:dyDescent="0.45"/>
+    <row r="58" x14ac:dyDescent="0.45"/>
+    <row r="59" x14ac:dyDescent="0.45"/>
+    <row r="60" x14ac:dyDescent="0.45"/>
+    <row r="61" x14ac:dyDescent="0.45"/>
+    <row r="62" x14ac:dyDescent="0.45"/>
+    <row r="63" x14ac:dyDescent="0.45"/>
+    <row r="64" x14ac:dyDescent="0.45"/>
+    <row r="65" x14ac:dyDescent="0.45"/>
+    <row r="66" x14ac:dyDescent="0.45"/>
+    <row r="67" x14ac:dyDescent="0.45"/>
+    <row r="68" x14ac:dyDescent="0.45"/>
+    <row r="69" x14ac:dyDescent="0.45"/>
+    <row r="70" x14ac:dyDescent="0.45"/>
+    <row r="71" x14ac:dyDescent="0.45"/>
+    <row r="72" x14ac:dyDescent="0.45"/>
+    <row r="73" x14ac:dyDescent="0.45"/>
+    <row r="74" x14ac:dyDescent="0.45"/>
+    <row r="75" x14ac:dyDescent="0.45"/>
+    <row r="76" x14ac:dyDescent="0.45"/>
+    <row r="77" x14ac:dyDescent="0.45"/>
+    <row r="78" x14ac:dyDescent="0.45"/>
+    <row r="79" x14ac:dyDescent="0.45"/>
+    <row r="80" x14ac:dyDescent="0.45"/>
+    <row r="81" x14ac:dyDescent="0.45"/>
+    <row r="82" x14ac:dyDescent="0.45"/>
+    <row r="83" x14ac:dyDescent="0.45"/>
+    <row r="84" x14ac:dyDescent="0.45"/>
+    <row r="85" x14ac:dyDescent="0.45"/>
+    <row r="86" x14ac:dyDescent="0.45"/>
+    <row r="87" x14ac:dyDescent="0.45"/>
+    <row r="88" x14ac:dyDescent="0.45"/>
+    <row r="89" x14ac:dyDescent="0.45"/>
+    <row r="90" x14ac:dyDescent="0.45"/>
+    <row r="91" x14ac:dyDescent="0.45"/>
+    <row r="92" x14ac:dyDescent="0.45"/>
+    <row r="93" x14ac:dyDescent="0.45"/>
+    <row r="94" x14ac:dyDescent="0.45"/>
+    <row r="95" x14ac:dyDescent="0.45"/>
+    <row r="96" x14ac:dyDescent="0.45"/>
+    <row r="97" x14ac:dyDescent="0.45"/>
+    <row r="98" x14ac:dyDescent="0.45"/>
+    <row r="99" x14ac:dyDescent="0.45"/>
+    <row r="100" x14ac:dyDescent="0.45"/>
+    <row r="101" x14ac:dyDescent="0.45"/>
+    <row r="102" x14ac:dyDescent="0.45"/>
+    <row r="103" x14ac:dyDescent="0.45"/>
+    <row r="104" x14ac:dyDescent="0.45"/>
+    <row r="105" x14ac:dyDescent="0.45"/>
+    <row r="106" x14ac:dyDescent="0.45"/>
+    <row r="107" x14ac:dyDescent="0.45"/>
+    <row r="108" x14ac:dyDescent="0.45"/>
+    <row r="109" x14ac:dyDescent="0.45"/>
+    <row r="110" x14ac:dyDescent="0.45"/>
+    <row r="111" x14ac:dyDescent="0.45"/>
+    <row r="112" x14ac:dyDescent="0.45"/>
+    <row r="113" x14ac:dyDescent="0.45"/>
+    <row r="114" x14ac:dyDescent="0.45"/>
+    <row r="115" x14ac:dyDescent="0.45"/>
+    <row r="116" x14ac:dyDescent="0.45"/>
+    <row r="117" x14ac:dyDescent="0.45"/>
+    <row r="118" x14ac:dyDescent="0.45"/>
+    <row r="119" x14ac:dyDescent="0.45"/>
+    <row r="120" x14ac:dyDescent="0.45"/>
+    <row r="121" x14ac:dyDescent="0.45"/>
+    <row r="122" x14ac:dyDescent="0.45"/>
+    <row r="123" x14ac:dyDescent="0.45"/>
+    <row r="124" x14ac:dyDescent="0.45"/>
+    <row r="125" x14ac:dyDescent="0.45"/>
+    <row r="126" x14ac:dyDescent="0.45"/>
+    <row r="127" x14ac:dyDescent="0.45"/>
+    <row r="128" x14ac:dyDescent="0.45"/>
+    <row r="129" x14ac:dyDescent="0.45"/>
+    <row r="130" x14ac:dyDescent="0.45"/>
+    <row r="131" x14ac:dyDescent="0.45"/>
+    <row r="132" x14ac:dyDescent="0.45"/>
+    <row r="133" x14ac:dyDescent="0.45"/>
+    <row r="134" x14ac:dyDescent="0.45"/>
+    <row r="135" x14ac:dyDescent="0.45"/>
+    <row r="136" x14ac:dyDescent="0.45"/>
+    <row r="137" x14ac:dyDescent="0.45"/>
+    <row r="138" x14ac:dyDescent="0.45"/>
+    <row r="139" x14ac:dyDescent="0.45"/>
+    <row r="140" x14ac:dyDescent="0.45"/>
+    <row r="141" x14ac:dyDescent="0.45"/>
+    <row r="142" x14ac:dyDescent="0.45"/>
+    <row r="143" x14ac:dyDescent="0.45"/>
+    <row r="144" x14ac:dyDescent="0.45"/>
+    <row r="145" x14ac:dyDescent="0.45"/>
+    <row r="146" x14ac:dyDescent="0.45"/>
+    <row r="147" x14ac:dyDescent="0.45"/>
+    <row r="148" x14ac:dyDescent="0.45"/>
+    <row r="149" x14ac:dyDescent="0.45"/>
+    <row r="150" x14ac:dyDescent="0.45"/>
+    <row r="151" x14ac:dyDescent="0.45"/>
+    <row r="152" x14ac:dyDescent="0.45"/>
+    <row r="153" x14ac:dyDescent="0.45"/>
+    <row r="154" x14ac:dyDescent="0.45"/>
+    <row r="155" x14ac:dyDescent="0.45"/>
+    <row r="156" x14ac:dyDescent="0.45"/>
+    <row r="157" x14ac:dyDescent="0.45"/>
+    <row r="158" x14ac:dyDescent="0.45"/>
+    <row r="159" x14ac:dyDescent="0.45"/>
+    <row r="160" x14ac:dyDescent="0.45"/>
+    <row r="161" x14ac:dyDescent="0.45"/>
+    <row r="162" x14ac:dyDescent="0.45"/>
+    <row r="163" x14ac:dyDescent="0.45"/>
+    <row r="164" x14ac:dyDescent="0.45"/>
+    <row r="165" x14ac:dyDescent="0.45"/>
+    <row r="166" x14ac:dyDescent="0.45"/>
+    <row r="167" x14ac:dyDescent="0.45"/>
+    <row r="168" x14ac:dyDescent="0.45"/>
+    <row r="169" x14ac:dyDescent="0.45"/>
+    <row r="170" x14ac:dyDescent="0.45"/>
+    <row r="171" x14ac:dyDescent="0.45"/>
+    <row r="172" x14ac:dyDescent="0.45"/>
+    <row r="173" x14ac:dyDescent="0.45"/>
+    <row r="174" x14ac:dyDescent="0.45"/>
+    <row r="175" x14ac:dyDescent="0.45"/>
+    <row r="176" x14ac:dyDescent="0.45"/>
+    <row r="177" x14ac:dyDescent="0.45"/>
+    <row r="178" x14ac:dyDescent="0.45"/>
+    <row r="179" x14ac:dyDescent="0.45"/>
+    <row r="180" x14ac:dyDescent="0.45"/>
+    <row r="181" x14ac:dyDescent="0.45"/>
+    <row r="182" x14ac:dyDescent="0.45"/>
+    <row r="183" x14ac:dyDescent="0.45"/>
+    <row r="184" x14ac:dyDescent="0.45"/>
+    <row r="185" x14ac:dyDescent="0.45"/>
+    <row r="186" x14ac:dyDescent="0.45"/>
+    <row r="187" x14ac:dyDescent="0.45"/>
+    <row r="188" x14ac:dyDescent="0.45"/>
+    <row r="189" x14ac:dyDescent="0.45"/>
+    <row r="190" x14ac:dyDescent="0.45"/>
+    <row r="191" x14ac:dyDescent="0.45"/>
+    <row r="192" x14ac:dyDescent="0.45"/>
+    <row r="193" x14ac:dyDescent="0.45"/>
+    <row r="194" x14ac:dyDescent="0.45"/>
+    <row r="195" x14ac:dyDescent="0.45"/>
+    <row r="196" x14ac:dyDescent="0.45"/>
+    <row r="197" x14ac:dyDescent="0.45"/>
+    <row r="198" x14ac:dyDescent="0.45"/>
+    <row r="199" x14ac:dyDescent="0.45"/>
+    <row r="200" x14ac:dyDescent="0.45"/>
   </sheetData>
+  <autoFilter ref="A1:T199" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="6">
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0000-000000000000}">
           <x14:formula1>
             <xm:f>LIST_DATA!$A$1:$A$9</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D999</xm:sqref>
+          <xm:sqref>D2:D986</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0000-000001000000}">
           <x14:formula1>
             <xm:f>LIST_DATA!$B$1:$B$6</xm:f>
           </x14:formula1>
-          <xm:sqref>J2:J999</xm:sqref>
+          <xm:sqref>J2:J986</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0000-000002000000}">
           <x14:formula1>
             <xm:f>LIST_DATA!$C$1:$C$15</xm:f>
           </x14:formula1>
-          <xm:sqref>I2:I999</xm:sqref>
+          <xm:sqref>I2:I986</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{354EFE19-C43E-4A2D-83B1-FD15C013476E}">
+          <x14:formula1>
+            <xm:f>LIST_DATA!$D:$D</xm:f>
+          </x14:formula1>
+          <xm:sqref>G2:G200</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{9DE71029-D453-4F4E-B557-CC5A72AEA9EB}">
+          <x14:formula1>
+            <xm:f>LIST_DATA!$E:$E</xm:f>
+          </x14:formula1>
+          <xm:sqref>P2:P200 S2:S200</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{262E53F9-7911-451D-88C9-1E420930ED84}">
+          <x14:formula1>
+            <xm:f>LIST_DATA!$F:$F</xm:f>
+          </x14:formula1>
+          <xm:sqref>E2:E200</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -1675,130 +1819,297 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="13.59765625" customWidth="1"/>
+    <col min="1" max="1" width="16.73046875" style="8" customWidth="1"/>
+    <col min="2" max="3" width="9.06640625" style="8"/>
+    <col min="4" max="4" width="14.46484375" style="8" customWidth="1"/>
+    <col min="5" max="5" width="17" customWidth="1"/>
+    <col min="6" max="6" width="49.53125" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A1" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A1" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C1">
+      <c r="C1" s="8">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
+      <c r="D1" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A2" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="8">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
+      <c r="D2" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A3" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="8">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
+      <c r="D3" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A4" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="8">
         <v>7</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
+      <c r="D4" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A5" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="8">
         <v>8</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
+      <c r="D5" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A6" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="8">
         <v>9</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
+      <c r="D6" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A7" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="8">
         <v>10</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
+      <c r="D7" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A8" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="8">
         <v>11</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
+      <c r="D8" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A9" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="8">
         <v>12</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="C10">
+      <c r="D9" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C10" s="8">
         <v>13</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="C11">
+      <c r="D10" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C11" s="8">
         <v>14</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="C12">
+      <c r="D11" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C12" s="8">
         <v>15</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="C13">
+      <c r="D12" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C13" s="8">
         <v>16</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="C14">
+      <c r="D13" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C14" s="8">
         <v>17</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="C15">
+      <c r="D14" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C15" s="8">
         <v>18</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="D16" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="17" spans="4:6" x14ac:dyDescent="0.45">
+      <c r="D17" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="18" spans="4:6" x14ac:dyDescent="0.45">
+      <c r="F18" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="19" spans="4:6" x14ac:dyDescent="0.45">
+      <c r="F19" s="8" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="20" spans="4:6" x14ac:dyDescent="0.45">
+      <c r="F20" s="8" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="21" spans="4:6" x14ac:dyDescent="0.45">
+      <c r="F21" s="8" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="22" spans="4:6" x14ac:dyDescent="0.45">
+      <c r="F22" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="23" spans="4:6" x14ac:dyDescent="0.45">
+      <c r="F23" s="8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="24" spans="4:6" x14ac:dyDescent="0.45">
+      <c r="F24" s="8" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="25" spans="4:6" x14ac:dyDescent="0.45">
+      <c r="F25" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="26" spans="4:6" x14ac:dyDescent="0.45">
+      <c r="F26" s="8" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
